--- a/fixtures/sanitized/m5/full-import-cutover.xlsx
+++ b/fixtures/sanitized/m5/full-import-cutover.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="150">
   <si>
     <t>template_version</t>
   </si>
@@ -39,7 +39,7 @@
     <t>ui_locale</t>
   </si>
   <si>
-    <t>ledgerkit-workbook-v1.3</t>
+    <t>ledgerkit-workbook-v1.4</t>
   </si>
   <si>
     <t>CNY</t>
@@ -219,6 +219,24 @@
     <t>display_label</t>
   </si>
   <si>
+    <t>fx_override_currency</t>
+  </si>
+  <si>
+    <t>fx_override_value</t>
+  </si>
+  <si>
+    <t>fx_override_reason</t>
+  </si>
+  <si>
+    <t>fee_fx_override_currency</t>
+  </si>
+  <si>
+    <t>fee_fx_override_value</t>
+  </si>
+  <si>
+    <t>fee_fx_override_reason</t>
+  </si>
+  <si>
     <t>Income</t>
   </si>
   <si>
@@ -256,6 +274,24 @@
   </si>
   <si>
     <t>to_amount</t>
+  </si>
+  <si>
+    <t>from_fx_override_currency</t>
+  </si>
+  <si>
+    <t>from_fx_override_value</t>
+  </si>
+  <si>
+    <t>from_fx_override_reason</t>
+  </si>
+  <si>
+    <t>to_fx_override_currency</t>
+  </si>
+  <si>
+    <t>to_fx_override_value</t>
+  </si>
+  <si>
+    <t>to_fx_override_reason</t>
   </si>
   <si>
     <t>settlement_account_legacy_id</t>
@@ -813,13 +849,13 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -827,13 +863,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
         <v>26</v>
@@ -854,16 +890,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="E1" t="s">
         <v>46</v>
@@ -874,13 +910,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
         <v>26</v>
@@ -899,10 +935,10 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -913,28 +949,28 @@
         <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="H1" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="I1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="J1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L1" t="s">
         <v>59</v>
@@ -943,42 +979,51 @@
         <v>55</v>
       </c>
       <c r="N1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="O1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>111</v>
+      </c>
+      <c r="P1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F2" t="s">
         <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="H2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -986,42 +1031,42 @@
         <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
         <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="L3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
         <v>23</v>
@@ -1030,10 +1075,10 @@
         <v>43</v>
       </c>
       <c r="H4" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I4" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1048,51 +1093,51 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D1" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E1" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="F1" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="G1" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H1" t="s">
         <v>18</v>
       </c>
       <c r="I1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
         <v>43</v>
@@ -1106,22 +1151,22 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H3" t="s">
         <v>26</v>
@@ -1142,30 +1187,30 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D1" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
         <v>39</v>
@@ -1173,13 +1218,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
         <v>39</v>
@@ -1187,13 +1232,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
         <v>39</v>
@@ -1201,13 +1246,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D5" t="s">
         <v>39</v>
@@ -1215,13 +1260,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D6" t="s">
         <v>43</v>
@@ -1232,10 +1277,10 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
         <v>39</v>
@@ -1243,33 +1288,33 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1284,36 +1329,36 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C1" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D1" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="E1" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F1" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
         <v>39</v>
@@ -1558,10 +1603,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -1604,8 +1649,26 @@
       <c r="N1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" t="s">
+        <v>66</v>
+      </c>
+      <c r="S1" t="s">
+        <v>67</v>
+      </c>
+      <c r="T1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1613,7 +1676,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -1622,33 +1685,33 @@
         <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s">
         <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="N2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -1657,22 +1720,22 @@
         <v>40</v>
       </c>
       <c r="F3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" t="s">
         <v>71</v>
       </c>
-      <c r="G3" t="s">
-        <v>65</v>
-      </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s">
         <v>38</v>
       </c>
       <c r="M3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="N3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1682,10 +1745,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -1693,16 +1756,25 @@
         <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E1" t="s">
         <v>55</v>
       </c>
       <c r="F1" t="s">
         <v>57</v>
+      </c>
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1712,10 +1784,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -1723,16 +1795,16 @@
         <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G1" t="s">
         <v>58</v>
@@ -1742,6 +1814,33 @@
       </c>
       <c r="I1" t="s">
         <v>57</v>
+      </c>
+      <c r="J1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1762,13 +1861,13 @@
         <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F1" t="s">
         <v>10</v>
@@ -1782,7 +1881,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -1791,10 +1890,10 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
